--- a/output/descriptif_nationalites_2024.xlsx
+++ b/output/descriptif_nationalites_2024.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="top_pays_moy_mobiles" sheetId="1" r:id="rId1"/>
-    <sheet name="top_pays_parts_2024" sheetId="2" r:id="rId2"/>
-    <sheet name="top10_effectifs_univ_com_inge" sheetId="3" r:id="rId3"/>
-    <sheet name="top10_parts_univ_com_inge" sheetId="4" r:id="rId4"/>
+    <sheet name="top_pays_2024" sheetId="2" r:id="rId2"/>
+    <sheet name="top_pays_parts_2024" sheetId="3" r:id="rId3"/>
+    <sheet name="top10_effectifs_univ_com_inge" sheetId="4" r:id="rId4"/>
+    <sheet name="top10_parts_univ_com_inge" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,18 +477,38 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nationalite</t>
+          <t>Nationalité</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>Effectifs 2024-2025</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Part 2024-2025</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Part 2021-2022</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Évolution 1 an</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Évolution 5 ans</t>
         </is>
       </c>
     </row>
@@ -498,7 +519,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.1083656139391454</v>
+        <v>35668</v>
+      </c>
+      <c r="C2">
+        <v>10.83656139391454</v>
+      </c>
+      <c r="D2">
+        <v>12.3892010238743</v>
+      </c>
+      <c r="E2">
+        <v>-3.118209474141678</v>
+      </c>
+      <c r="F2">
+        <v>-2.35703139970982</v>
       </c>
     </row>
     <row r="3">
@@ -508,7 +541,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.08408148384450623</v>
+        <v>27675</v>
+      </c>
+      <c r="C3">
+        <v>8.408148384450623</v>
+      </c>
+      <c r="D3">
+        <v>8.300787224109342</v>
+      </c>
+      <c r="E3">
+        <v>0.6766342900796682</v>
+      </c>
+      <c r="F3">
+        <v>14.03906378770397</v>
       </c>
     </row>
     <row r="4">
@@ -518,7 +563,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.07052514849078674</v>
+        <v>23213</v>
+      </c>
+      <c r="C4">
+        <v>7.052514849078674</v>
+      </c>
+      <c r="D4">
+        <v>7.316515607643641</v>
+      </c>
+      <c r="E4">
+        <v>-3.975345412426574</v>
+      </c>
+      <c r="F4">
+        <v>-15.01738971261212</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +585,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.04896929924501359</v>
+        <v>16118</v>
+      </c>
+      <c r="C5">
+        <v>4.896929924501359</v>
+      </c>
+      <c r="D5">
+        <v>4.394610171128677</v>
+      </c>
+      <c r="E5">
+        <v>5.851448085637355</v>
+      </c>
+      <c r="F5">
+        <v>36.26986810957051</v>
       </c>
     </row>
     <row r="6">
@@ -538,7 +607,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.04070242598246973</v>
+        <v>13397</v>
+      </c>
+      <c r="C6">
+        <v>4.070242598246973</v>
+      </c>
+      <c r="D6">
+        <v>4.278377899769789</v>
+      </c>
+      <c r="E6">
+        <v>0.8810240963855421</v>
+      </c>
+      <c r="F6">
+        <v>14.09470277635837</v>
       </c>
     </row>
     <row r="7">
@@ -548,7 +629,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.03946285071928785</v>
+        <v>12989</v>
+      </c>
+      <c r="C7">
+        <v>3.946285071928785</v>
+      </c>
+      <c r="D7">
+        <v>3.784793212808088</v>
+      </c>
+      <c r="E7">
+        <v>4.371233427079148</v>
+      </c>
+      <c r="F7">
+        <v>18.44792996534744</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +651,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.03086177824363123</v>
+        <v>10158</v>
+      </c>
+      <c r="C8">
+        <v>3.086177824363122</v>
+      </c>
+      <c r="D8">
+        <v>2.431540480061819</v>
+      </c>
+      <c r="E8">
+        <v>18.07509008485412</v>
+      </c>
+      <c r="F8">
+        <v>72.99046321525886</v>
       </c>
     </row>
     <row r="9">
@@ -568,7 +673,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.03068860228774552</v>
+        <v>10101</v>
+      </c>
+      <c r="C9">
+        <v>3.068860228774553</v>
+      </c>
+      <c r="D9">
+        <v>2.744176312442649</v>
+      </c>
+      <c r="E9">
+        <v>9.984756097560975</v>
+      </c>
+      <c r="F9">
+        <v>31.62627052384676</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +695,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.02875328502635616</v>
+        <v>9464</v>
+      </c>
+      <c r="C10">
+        <v>2.875328502635616</v>
+      </c>
+      <c r="D10">
+        <v>3.441247967545116</v>
+      </c>
+      <c r="E10">
+        <v>-7.6232308443143</v>
+      </c>
+      <c r="F10">
+        <v>58.71205768908268</v>
       </c>
     </row>
     <row r="11">
@@ -588,7 +717,4146 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.02551459083382704</v>
+        <v>8398</v>
+      </c>
+      <c r="C11">
+        <v>2.551459083382703</v>
+      </c>
+      <c r="D11">
+        <v>2.125988054799813</v>
+      </c>
+      <c r="E11">
+        <v>14.35185185185185</v>
+      </c>
+      <c r="F11">
+        <v>32.00251493241119</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BENIN</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>7753</v>
+      </c>
+      <c r="C12">
+        <v>2.355496817512039</v>
+      </c>
+      <c r="D12">
+        <v>1.642706505465492</v>
+      </c>
+      <c r="E12">
+        <v>23.23954856143697</v>
+      </c>
+      <c r="F12">
+        <v>128.9046353705344</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ALLEMAGNE</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>6952</v>
+      </c>
+      <c r="C13">
+        <v>2.112139026872655</v>
+      </c>
+      <c r="D13">
+        <v>2.326577265482879</v>
+      </c>
+      <c r="E13">
+        <v>-0.5863005863005863</v>
+      </c>
+      <c r="F13">
+        <v>0.9145013790100159</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ESPAGNE</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>6487</v>
+      </c>
+      <c r="C14">
+        <v>1.970863904965896</v>
+      </c>
+      <c r="D14">
+        <v>2.231273242429609</v>
+      </c>
+      <c r="E14">
+        <v>-0.1539171925504079</v>
+      </c>
+      <c r="F14">
+        <v>2.302475950165589</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CONGO</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>6319</v>
+      </c>
+      <c r="C15">
+        <v>1.919822570599584</v>
+      </c>
+      <c r="D15">
+        <v>1.661702915465975</v>
+      </c>
+      <c r="E15">
+        <v>6.848156915793034</v>
+      </c>
+      <c r="F15">
+        <v>71.061180292366</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ETATS-UNIS</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>5483</v>
+      </c>
+      <c r="C16">
+        <v>1.665831168633885</v>
+      </c>
+      <c r="D16">
+        <v>1.885152212759792</v>
+      </c>
+      <c r="E16">
+        <v>-6.73583942847423</v>
+      </c>
+      <c r="F16">
+        <v>-5.006930006930007</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TOGO</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>5259</v>
+      </c>
+      <c r="C17">
+        <v>1.597776056145468</v>
+      </c>
+      <c r="D17">
+        <v>1.314615966643592</v>
+      </c>
+      <c r="E17">
+        <v>11.77470775770457</v>
+      </c>
+      <c r="F17">
+        <v>73.39268051434223</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VIETNAM</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>5107</v>
+      </c>
+      <c r="C18">
+        <v>1.551595801242613</v>
+      </c>
+      <c r="D18">
+        <v>1.559637458344737</v>
+      </c>
+      <c r="E18">
+        <v>4.181966544267645</v>
+      </c>
+      <c r="F18">
+        <v>-2.351816443594646</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MADAGASCAR</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>4818</v>
+      </c>
+      <c r="C19">
+        <v>1.463792553433897</v>
+      </c>
+      <c r="D19">
+        <v>1.235410596133104</v>
+      </c>
+      <c r="E19">
+        <v>13.71253245220675</v>
+      </c>
+      <c r="F19">
+        <v>49.53445065176908</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BRESIL</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>4800</v>
+      </c>
+      <c r="C20">
+        <v>1.458323839037506</v>
+      </c>
+      <c r="D20">
+        <v>1.561247323599015</v>
+      </c>
+      <c r="E20">
+        <v>3.96361273554256</v>
+      </c>
+      <c r="F20">
+        <v>-3.089036947304664</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GABON</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>4579</v>
+      </c>
+      <c r="C21">
+        <v>1.391180178948488</v>
+      </c>
+      <c r="D21">
+        <v>1.442761240884138</v>
+      </c>
+      <c r="E21">
+        <v>0.4607283896445809</v>
+      </c>
+      <c r="F21">
+        <v>5.7261602401293</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TURQUIE</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>3765</v>
+      </c>
+      <c r="C22">
+        <v>1.143872761245044</v>
+      </c>
+      <c r="D22">
+        <v>0.9591577184989616</v>
+      </c>
+      <c r="E22">
+        <v>12.7920910724985</v>
+      </c>
+      <c r="F22">
+        <v>48.5207100591716</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RUSSIE</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>3391</v>
+      </c>
+      <c r="C23">
+        <v>1.030245028786705</v>
+      </c>
+      <c r="D23">
+        <v>1.044158603924852</v>
+      </c>
+      <c r="E23">
+        <v>-0.4403992953611274</v>
+      </c>
+      <c r="F23">
+        <v>-5.332216638749302</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GRECE</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>3323</v>
+      </c>
+      <c r="C24">
+        <v>1.009585441067007</v>
+      </c>
+      <c r="D24">
+        <v>0.9778321554485889</v>
+      </c>
+      <c r="E24">
+        <v>4.727387330601954</v>
+      </c>
+      <c r="F24">
+        <v>38.74739039665971</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GUINEE</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>3310</v>
+      </c>
+      <c r="C25">
+        <v>1.005635814002947</v>
+      </c>
+      <c r="D25">
+        <v>0.9150474105317385</v>
+      </c>
+      <c r="E25">
+        <v>14.21670117322291</v>
+      </c>
+      <c r="F25">
+        <v>-8.28484344693821</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>UKRAINE</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>3310</v>
+      </c>
+      <c r="C26">
+        <v>1.005635814002947</v>
+      </c>
+      <c r="D26">
+        <v>0.8725469678187936</v>
+      </c>
+      <c r="E26">
+        <v>6.84312459651388</v>
+      </c>
+      <c r="F26">
+        <v>155.9938128383604</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>COLOMBIE</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>3265</v>
+      </c>
+      <c r="C27">
+        <v>0.9919640280119704</v>
+      </c>
+      <c r="D27">
+        <v>1.189368449860747</v>
+      </c>
+      <c r="E27">
+        <v>-7.716223855285471</v>
+      </c>
+      <c r="F27">
+        <v>-18.6799501867995</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IRAN</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>3255</v>
+      </c>
+      <c r="C28">
+        <v>0.988925853347309</v>
+      </c>
+      <c r="D28">
+        <v>0.7585685078158958</v>
+      </c>
+      <c r="E28">
+        <v>20.24381233838197</v>
+      </c>
+      <c r="F28">
+        <v>56.11510791366906</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BELGIQUE</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>3144</v>
+      </c>
+      <c r="C29">
+        <v>0.9552021145695666</v>
+      </c>
+      <c r="D29">
+        <v>0.9520743113801374</v>
+      </c>
+      <c r="E29">
+        <v>4.904904904904905</v>
+      </c>
+      <c r="F29">
+        <v>16.22920517560074</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AUTRE PAYS, ETRANGER SANS AUTRE INDICATION</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>2776</v>
+      </c>
+      <c r="C30">
+        <v>0.8433972869100245</v>
+      </c>
+      <c r="D30">
+        <v>0.7907658129014601</v>
+      </c>
+      <c r="E30">
+        <v>31.43939393939394</v>
+      </c>
+      <c r="F30">
+        <v>-3.711411723898717</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MEXIQUE</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>2702</v>
+      </c>
+      <c r="C31">
+        <v>0.8209147943915295</v>
+      </c>
+      <c r="D31">
+        <v>0.9366196049390665</v>
+      </c>
+      <c r="E31">
+        <v>-5.755144750610394</v>
+      </c>
+      <c r="F31">
+        <v>-11.4388725008194</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ROUMANIE</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>2673</v>
+      </c>
+      <c r="C32">
+        <v>0.8121040878640113</v>
+      </c>
+      <c r="D32">
+        <v>0.7698375645958433</v>
+      </c>
+      <c r="E32">
+        <v>6.155679110405083</v>
+      </c>
+      <c r="F32">
+        <v>2.649769585253456</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EGYPTE</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>2619</v>
+      </c>
+      <c r="C33">
+        <v>0.7956979446748393</v>
+      </c>
+      <c r="D33">
+        <v>0.7727353220535441</v>
+      </c>
+      <c r="E33">
+        <v>2.6656213249706</v>
+      </c>
+      <c r="F33">
+        <v>17.86678667866787</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TCHAD</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>2544</v>
+      </c>
+      <c r="C34">
+        <v>0.7729116346898783</v>
+      </c>
+      <c r="D34">
+        <v>0.8625658032422686</v>
+      </c>
+      <c r="E34">
+        <v>-0.5084082909659757</v>
+      </c>
+      <c r="F34">
+        <v>64.34108527131784</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MALI</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>2194</v>
+      </c>
+      <c r="C35">
+        <v>0.6665755214267268</v>
+      </c>
+      <c r="D35">
+        <v>0.7324886906965887</v>
+      </c>
+      <c r="E35">
+        <v>-2.402135231316726</v>
+      </c>
+      <c r="F35">
+        <v>-12.9019452163557</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>HAITI</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>2179</v>
+      </c>
+      <c r="C36">
+        <v>0.6620182594297346</v>
+      </c>
+      <c r="D36">
+        <v>0.8828501054461741</v>
+      </c>
+      <c r="E36">
+        <v>-13.66877971473851</v>
+      </c>
+      <c r="F36">
+        <v>24.230330672748</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>COREE DU SUD</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>2086</v>
+      </c>
+      <c r="C37">
+        <v>0.6337632350483829</v>
+      </c>
+      <c r="D37">
+        <v>0.7605003461210297</v>
+      </c>
+      <c r="E37">
+        <v>-5.52536231884058</v>
+      </c>
+      <c r="F37">
+        <v>-26.49753347427766</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ROYAUME-UNI</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>2014</v>
+      </c>
+      <c r="C38">
+        <v>0.6118883774628203</v>
+      </c>
+      <c r="D38">
+        <v>0.644590047812998</v>
+      </c>
+      <c r="E38">
+        <v>5.22466039707419</v>
+      </c>
+      <c r="F38">
+        <v>-3.312530004800768</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CANADA</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>1980</v>
+      </c>
+      <c r="C39">
+        <v>0.6015585836029713</v>
+      </c>
+      <c r="D39">
+        <v>0.6030555242526201</v>
+      </c>
+      <c r="E39">
+        <v>2.590673575129534</v>
+      </c>
+      <c r="F39">
+        <v>11.42374788970175</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BURKINA</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>1980</v>
+      </c>
+      <c r="C40">
+        <v>0.6015585836029713</v>
+      </c>
+      <c r="D40">
+        <v>0.6957837628990453</v>
+      </c>
+      <c r="E40">
+        <v>-1.098901098901099</v>
+      </c>
+      <c r="F40">
+        <v>4.540654699049631</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>REP. DEM. CONGO</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>1959</v>
+      </c>
+      <c r="C41">
+        <v>0.5951784168071823</v>
+      </c>
+      <c r="D41">
+        <v>0.5129030700130399</v>
+      </c>
+      <c r="E41">
+        <v>13.17157712305026</v>
+      </c>
+      <c r="F41">
+        <v>53.04687500000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ARMENIE</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>1951</v>
+      </c>
+      <c r="C42">
+        <v>0.5927478770754531</v>
+      </c>
+      <c r="D42">
+        <v>0.4011784213661317</v>
+      </c>
+      <c r="E42">
+        <v>18.746195982958</v>
+      </c>
+      <c r="F42">
+        <v>86.69856459330143</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PORTUGAL</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>1668</v>
+      </c>
+      <c r="C43">
+        <v>0.5067675340655334</v>
+      </c>
+      <c r="D43">
+        <v>0.5022779593348037</v>
+      </c>
+      <c r="E43">
+        <v>2.583025830258303</v>
+      </c>
+      <c r="F43">
+        <v>15.19337016574586</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>COMORES</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>1645</v>
+      </c>
+      <c r="C44">
+        <v>0.4997797323368121</v>
+      </c>
+      <c r="D44">
+        <v>0.5315775069626673</v>
+      </c>
+      <c r="E44">
+        <v>-0.7840772014475271</v>
+      </c>
+      <c r="F44">
+        <v>17.58398856325947</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SUISSE</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>1614</v>
+      </c>
+      <c r="C45">
+        <v>0.4903613908763615</v>
+      </c>
+      <c r="D45">
+        <v>0.5029219054365149</v>
+      </c>
+      <c r="E45">
+        <v>3.395259449071109</v>
+      </c>
+      <c r="F45">
+        <v>13.34269662921348</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LUXEMBOURG</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>1604</v>
+      </c>
+      <c r="C46">
+        <v>0.4873232162117</v>
+      </c>
+      <c r="D46">
+        <v>0.4662169776389716</v>
+      </c>
+      <c r="E46">
+        <v>3.886010362694301</v>
+      </c>
+      <c r="F46">
+        <v>17.50915750915751</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>POLOGNE</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>1512</v>
+      </c>
+      <c r="C47">
+        <v>0.4593720092968144</v>
+      </c>
+      <c r="D47">
+        <v>0.4572017322150136</v>
+      </c>
+      <c r="E47">
+        <v>2.578018995929444</v>
+      </c>
+      <c r="F47">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>JAPON</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>1448</v>
+      </c>
+      <c r="C48">
+        <v>0.4399276914429811</v>
+      </c>
+      <c r="D48">
+        <v>0.4546259478081685</v>
+      </c>
+      <c r="E48">
+        <v>0.3465003465003465</v>
+      </c>
+      <c r="F48">
+        <v>-12.34866828087167</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MAURICE</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>1206</v>
+      </c>
+      <c r="C49">
+        <v>0.3664038645581734</v>
+      </c>
+      <c r="D49">
+        <v>0.3986026369592865</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>-18.67835468644639</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SYRIE</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>1156</v>
+      </c>
+      <c r="C50">
+        <v>0.351212991234866</v>
+      </c>
+      <c r="D50">
+        <v>0.4501183250961894</v>
+      </c>
+      <c r="E50">
+        <v>-7.297514033680834</v>
+      </c>
+      <c r="F50">
+        <v>-37.47971876690103</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BURUNDI</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>1125</v>
+      </c>
+      <c r="C51">
+        <v>0.3417946497744155</v>
+      </c>
+      <c r="D51">
+        <v>0.3628636283143101</v>
+      </c>
+      <c r="E51">
+        <v>-0.7936507936507936</v>
+      </c>
+      <c r="F51">
+        <v>115.5172413793103</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TAIWAN</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>1076</v>
+      </c>
+      <c r="C52">
+        <v>0.3269075939175743</v>
+      </c>
+      <c r="D52">
+        <v>0.3103820210248402</v>
+      </c>
+      <c r="E52">
+        <v>-0.7380073800738007</v>
+      </c>
+      <c r="F52">
+        <v>-6.759098786828423</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PEROU</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>1039</v>
+      </c>
+      <c r="C53">
+        <v>0.3156663476583269</v>
+      </c>
+      <c r="D53">
+        <v>0.3396815686527038</v>
+      </c>
+      <c r="E53">
+        <v>1.070038910505837</v>
+      </c>
+      <c r="F53">
+        <v>-6.899641577060931</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AZERBAIDJAN</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>1036</v>
+      </c>
+      <c r="C54">
+        <v>0.3147548952589284</v>
+      </c>
+      <c r="D54">
+        <v>0.3016887486517379</v>
+      </c>
+      <c r="E54">
+        <v>9.862142099681867</v>
+      </c>
+      <c r="F54">
+        <v>35.95800524934383</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PAKISTAN</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>1034</v>
+      </c>
+      <c r="C55">
+        <v>0.3141472603259961</v>
+      </c>
+      <c r="D55">
+        <v>0.1757972857671813</v>
+      </c>
+      <c r="E55">
+        <v>58.58895705521472</v>
+      </c>
+      <c r="F55">
+        <v>83.33333333333334</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MAURITANIE</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>1022</v>
+      </c>
+      <c r="C56">
+        <v>0.3105014507284024</v>
+      </c>
+      <c r="D56">
+        <v>0.2939613954312024</v>
+      </c>
+      <c r="E56">
+        <v>14.18994413407821</v>
+      </c>
+      <c r="F56">
+        <v>4.17940876656473</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>INDONESIE</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>1011</v>
+      </c>
+      <c r="C57">
+        <v>0.3071594585972748</v>
+      </c>
+      <c r="D57">
+        <v>0.3090941288214176</v>
+      </c>
+      <c r="E57">
+        <v>5.3125</v>
+      </c>
+      <c r="F57">
+        <v>4.984423676012461</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NIGERIA</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>992</v>
+      </c>
+      <c r="C58">
+        <v>0.301386926734418</v>
+      </c>
+      <c r="D58">
+        <v>0.2797945811935541</v>
+      </c>
+      <c r="E58">
+        <v>14.68208092485549</v>
+      </c>
+      <c r="F58">
+        <v>61.03896103896103</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>IRLANDE</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>931</v>
+      </c>
+      <c r="C59">
+        <v>0.282854061279983</v>
+      </c>
+      <c r="D59">
+        <v>0.2739990662781525</v>
+      </c>
+      <c r="E59">
+        <v>12.43961352657005</v>
+      </c>
+      <c r="F59">
+        <v>35.71428571428572</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PAYS-BAS</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>815</v>
+      </c>
+      <c r="C60">
+        <v>0.2476112351699099</v>
+      </c>
+      <c r="D60">
+        <v>0.277218796786709</v>
+      </c>
+      <c r="E60">
+        <v>0.3694581280788177</v>
+      </c>
+      <c r="F60">
+        <v>23.86018237082067</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CHILI</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>787</v>
+      </c>
+      <c r="C61">
+        <v>0.2391043461088578</v>
+      </c>
+      <c r="D61">
+        <v>0.2662717130576171</v>
+      </c>
+      <c r="E61">
+        <v>-5.408653846153847</v>
+      </c>
+      <c r="F61">
+        <v>-3.789731051344743</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>NIGER</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>756</v>
+      </c>
+      <c r="C62">
+        <v>0.2296860046484072</v>
+      </c>
+      <c r="D62">
+        <v>0.3467649757715279</v>
+      </c>
+      <c r="E62">
+        <v>-15.625</v>
+      </c>
+      <c r="F62">
+        <v>-27.30769230769231</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SUEDE</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>755</v>
+      </c>
+      <c r="C63">
+        <v>0.2293821871819411</v>
+      </c>
+      <c r="D63">
+        <v>0.2253811355989504</v>
+      </c>
+      <c r="E63">
+        <v>8.946608946608947</v>
+      </c>
+      <c r="F63">
+        <v>52.834008097166</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BULGARIE</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>750</v>
+      </c>
+      <c r="C64">
+        <v>0.2278630998496104</v>
+      </c>
+      <c r="D64">
+        <v>0.2137901057681472</v>
+      </c>
+      <c r="E64">
+        <v>12.27544910179641</v>
+      </c>
+      <c r="F64">
+        <v>-11.76470588235294</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AFGHANISTAN</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>712</v>
+      </c>
+      <c r="C65">
+        <v>0.2163180361238968</v>
+      </c>
+      <c r="D65">
+        <v>0.1619524445803886</v>
+      </c>
+      <c r="E65">
+        <v>8.868501529051988</v>
+      </c>
+      <c r="F65">
+        <v>148.0836236933798</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DJIBOUTI</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>711</v>
+      </c>
+      <c r="C66">
+        <v>0.2160142186574306</v>
+      </c>
+      <c r="D66">
+        <v>0.2041309142424779</v>
+      </c>
+      <c r="E66">
+        <v>7.564296520423601</v>
+      </c>
+      <c r="F66">
+        <v>-10.678391959799</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CAMBODGE</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>692</v>
+      </c>
+      <c r="C67">
+        <v>0.2102416867945738</v>
+      </c>
+      <c r="D67">
+        <v>0.2050968333950448</v>
+      </c>
+      <c r="E67">
+        <v>39.7979797979798</v>
+      </c>
+      <c r="F67">
+        <v>-5.33515731874145</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MALAISIE</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>679</v>
+      </c>
+      <c r="C68">
+        <v>0.2062920597305139</v>
+      </c>
+      <c r="D68">
+        <v>0.2234492972938165</v>
+      </c>
+      <c r="E68">
+        <v>3.191489361702128</v>
+      </c>
+      <c r="F68">
+        <v>-11.58854166666667</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>HONGRIE</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>643</v>
+      </c>
+      <c r="C69">
+        <v>0.1953546309377326</v>
+      </c>
+      <c r="D69">
+        <v>0.1774071510214595</v>
+      </c>
+      <c r="E69">
+        <v>9.914529914529915</v>
+      </c>
+      <c r="F69">
+        <v>41.31868131868131</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EQUATEUR</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>624</v>
+      </c>
+      <c r="C70">
+        <v>0.1895820990748758</v>
+      </c>
+      <c r="D70">
+        <v>0.1967255340727981</v>
+      </c>
+      <c r="E70">
+        <v>0.8077544426494345</v>
+      </c>
+      <c r="F70">
+        <v>15.34195933456562</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ARGENTINE</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>621</v>
+      </c>
+      <c r="C71">
+        <v>0.1886706466754774</v>
+      </c>
+      <c r="D71">
+        <v>0.2472753030571341</v>
+      </c>
+      <c r="E71">
+        <v>-5.623100303951368</v>
+      </c>
+      <c r="F71">
+        <v>-28.70264064293915</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>KAZAKHSTAN</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>594</v>
+      </c>
+      <c r="C72">
+        <v>0.1804675750808914</v>
+      </c>
+      <c r="D72">
+        <v>0.1693578247500684</v>
+      </c>
+      <c r="E72">
+        <v>8.196721311475409</v>
+      </c>
+      <c r="F72">
+        <v>4.028021015761821</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>NORVEGE</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>590</v>
+      </c>
+      <c r="C73">
+        <v>0.1792523052150268</v>
+      </c>
+      <c r="D73">
+        <v>0.1790170162757377</v>
+      </c>
+      <c r="E73">
+        <v>5.734767025089606</v>
+      </c>
+      <c r="F73">
+        <v>35.3211009174312</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>VENEZUELA</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>584</v>
+      </c>
+      <c r="C74">
+        <v>0.1774294004162299</v>
+      </c>
+      <c r="D74">
+        <v>0.2092824830561682</v>
+      </c>
+      <c r="E74">
+        <v>-4.730831973898858</v>
+      </c>
+      <c r="F74">
+        <v>-23.56020942408377</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>REP. CENTRAFRICAINE</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>565</v>
+      </c>
+      <c r="C75">
+        <v>0.1716568685533731</v>
+      </c>
+      <c r="D75">
+        <v>0.1593766601735435</v>
+      </c>
+      <c r="E75">
+        <v>7.824427480916031</v>
+      </c>
+      <c r="F75">
+        <v>9.496124031007753</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AUTRICHE</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>539</v>
+      </c>
+      <c r="C76">
+        <v>0.1637576144252533</v>
+      </c>
+      <c r="D76">
+        <v>0.1835246389877167</v>
+      </c>
+      <c r="E76">
+        <v>-4.770318021201414</v>
+      </c>
+      <c r="F76">
+        <v>7.370517928286853</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>GEORGIE</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>536</v>
+      </c>
+      <c r="C77">
+        <v>0.1628461620258549</v>
+      </c>
+      <c r="D77">
+        <v>0.1213838401725776</v>
+      </c>
+      <c r="E77">
+        <v>14.52991452991453</v>
+      </c>
+      <c r="F77">
+        <v>39.94778067885117</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ARABIE SAOUDITE</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>529</v>
+      </c>
+      <c r="C78">
+        <v>0.1607194397605918</v>
+      </c>
+      <c r="D78">
+        <v>0.1915739652591078</v>
+      </c>
+      <c r="E78">
+        <v>-4.684684684684685</v>
+      </c>
+      <c r="F78">
+        <v>-3.113553113553114</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ALBANIE</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>515</v>
+      </c>
+      <c r="C79">
+        <v>0.1564659952300658</v>
+      </c>
+      <c r="D79">
+        <v>0.1799829354283047</v>
+      </c>
+      <c r="E79">
+        <v>-9.807355516637479</v>
+      </c>
+      <c r="F79">
+        <v>-22.78860569715143</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>REPUBLIQUE TCHEQUE</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>514</v>
+      </c>
+      <c r="C80">
+        <v>0.1561621777635996</v>
+      </c>
+      <c r="D80">
+        <v>0.161630471529533</v>
+      </c>
+      <c r="E80">
+        <v>5.544147843942506</v>
+      </c>
+      <c r="F80">
+        <v>2.390438247011952</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>GHANA</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>473</v>
+      </c>
+      <c r="C81">
+        <v>0.1437056616384876</v>
+      </c>
+      <c r="D81">
+        <v>0.1387703849187823</v>
+      </c>
+      <c r="E81">
+        <v>3.956043956043956</v>
+      </c>
+      <c r="F81">
+        <v>9.237875288683602</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ANGOLA</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>413</v>
+      </c>
+      <c r="C82">
+        <v>0.1254766136505188</v>
+      </c>
+      <c r="D82">
+        <v>0.1226717323760001</v>
+      </c>
+      <c r="E82">
+        <v>-2.59433962264151</v>
+      </c>
+      <c r="F82">
+        <v>-5.922551252847381</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>AUSTRALIE</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>397</v>
+      </c>
+      <c r="C83">
+        <v>0.1206155341870604</v>
+      </c>
+      <c r="D83">
+        <v>0.09820178051097124</v>
+      </c>
+      <c r="E83">
+        <v>2.31958762886598</v>
+      </c>
+      <c r="F83">
+        <v>2.056555269922879</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BOLIVIE</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>393</v>
+      </c>
+      <c r="C84">
+        <v>0.1194002643211958</v>
+      </c>
+      <c r="D84">
+        <v>0.119130028816588</v>
+      </c>
+      <c r="E84">
+        <v>3.421052631578948</v>
+      </c>
+      <c r="F84">
+        <v>6.793478260869565</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>THAILANDE</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>373</v>
+      </c>
+      <c r="C85">
+        <v>0.1133239149918729</v>
+      </c>
+      <c r="D85">
+        <v>0.1358726274610815</v>
+      </c>
+      <c r="E85">
+        <v>-9.685230024213075</v>
+      </c>
+      <c r="F85">
+        <v>-14.44954128440367</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BANGLADESH</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>373</v>
+      </c>
+      <c r="C86">
+        <v>0.1133239149918729</v>
+      </c>
+      <c r="D86">
+        <v>0.1049632145789397</v>
+      </c>
+      <c r="E86">
+        <v>6.571428571428571</v>
+      </c>
+      <c r="F86">
+        <v>115.606936416185</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>RWANDA</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>367</v>
+      </c>
+      <c r="C87">
+        <v>0.111501010193076</v>
+      </c>
+      <c r="D87">
+        <v>0.1068950528840736</v>
+      </c>
+      <c r="E87">
+        <v>3.966005665722379</v>
+      </c>
+      <c r="F87">
+        <v>3.380281690140845</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PHILIPPINES</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>345</v>
+      </c>
+      <c r="C88">
+        <v>0.1048170259308208</v>
+      </c>
+      <c r="D88">
+        <v>0.1271793550879791</v>
+      </c>
+      <c r="E88">
+        <v>-11.08247422680412</v>
+      </c>
+      <c r="F88">
+        <v>16.94915254237288</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>FINLANDE</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>339</v>
+      </c>
+      <c r="C89">
+        <v>0.1029941211320239</v>
+      </c>
+      <c r="D89">
+        <v>0.1194520018674437</v>
+      </c>
+      <c r="E89">
+        <v>0.5934718100890208</v>
+      </c>
+      <c r="F89">
+        <v>11.51315789473684</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ETHIOPIE</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>338</v>
+      </c>
+      <c r="C90">
+        <v>0.1026903036655577</v>
+      </c>
+      <c r="D90">
+        <v>0.08628877762931243</v>
+      </c>
+      <c r="E90">
+        <v>19.43462897526502</v>
+      </c>
+      <c r="F90">
+        <v>40.24896265560166</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SERBIE</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>334</v>
+      </c>
+      <c r="C91">
+        <v>0.1014750337996932</v>
+      </c>
+      <c r="D91">
+        <v>0.1168762174605985</v>
+      </c>
+      <c r="E91">
+        <v>2.45398773006135</v>
+      </c>
+      <c r="F91">
+        <v>-20.85308056872038</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>EMIRATS ARABES UNIS</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>334</v>
+      </c>
+      <c r="C92">
+        <v>0.1014750337996932</v>
+      </c>
+      <c r="D92">
+        <v>0.08371299322246728</v>
+      </c>
+      <c r="E92">
+        <v>10.96345514950166</v>
+      </c>
+      <c r="F92">
+        <v>312.3456790123457</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SLOVAQUIE</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>320</v>
+      </c>
+      <c r="C93">
+        <v>0.09722158926916707</v>
+      </c>
+      <c r="D93">
+        <v>0.08854258898530193</v>
+      </c>
+      <c r="E93">
+        <v>12.67605633802817</v>
+      </c>
+      <c r="F93">
+        <v>18.08118081180812</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ANDORRE</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>277</v>
+      </c>
+      <c r="C94">
+        <v>0.08415743821112276</v>
+      </c>
+      <c r="D94">
+        <v>0.1020654571212389</v>
+      </c>
+      <c r="E94">
+        <v>-4.152249134948097</v>
+      </c>
+      <c r="F94">
+        <v>-18.7683284457478</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SINGAPOUR</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>272</v>
+      </c>
+      <c r="C95">
+        <v>0.08263835087879202</v>
+      </c>
+      <c r="D95">
+        <v>0.09498205000241479</v>
+      </c>
+      <c r="E95">
+        <v>-2.857142857142857</v>
+      </c>
+      <c r="F95">
+        <v>16.7381974248927</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>NEPAL</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>271</v>
+      </c>
+      <c r="C96">
+        <v>0.08233453341232587</v>
+      </c>
+      <c r="D96">
+        <v>0.05280358034032551</v>
+      </c>
+      <c r="E96">
+        <v>40.41450777202073</v>
+      </c>
+      <c r="F96">
+        <v>34.82587064676617</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>LITUANIE</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>271</v>
+      </c>
+      <c r="C97">
+        <v>0.08233453341232587</v>
+      </c>
+      <c r="D97">
+        <v>0.09111837339214708</v>
+      </c>
+      <c r="E97">
+        <v>0.7434944237918215</v>
+      </c>
+      <c r="F97">
+        <v>7.53968253968254</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DANEMARK</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>262</v>
+      </c>
+      <c r="C98">
+        <v>0.07960017621413056</v>
+      </c>
+      <c r="D98">
+        <v>0.09337218474813658</v>
+      </c>
+      <c r="E98">
+        <v>-5.072463768115942</v>
+      </c>
+      <c r="F98">
+        <v>3.968253968253968</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SALVADOR</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>246</v>
+      </c>
+      <c r="C99">
+        <v>0.0747390967506722</v>
+      </c>
+      <c r="D99">
+        <v>0.07244393644251976</v>
+      </c>
+      <c r="E99">
+        <v>6.956521739130435</v>
+      </c>
+      <c r="F99">
+        <v>28.79581151832461</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>QATAR</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>245</v>
+      </c>
+      <c r="C100">
+        <v>0.07443527928420604</v>
+      </c>
+      <c r="D100">
+        <v>0.05151568813690294</v>
+      </c>
+      <c r="E100">
+        <v>8.888888888888889</v>
+      </c>
+      <c r="F100">
+        <v>152.5773195876289</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AFRIQUE DU SUD</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>241</v>
+      </c>
+      <c r="C101">
+        <v>0.07322000941834146</v>
+      </c>
+      <c r="D101">
+        <v>0.08661075068016806</v>
+      </c>
+      <c r="E101">
+        <v>-6.589147286821706</v>
+      </c>
+      <c r="F101">
+        <v>4.329004329004329</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CHYPRE</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>240</v>
+      </c>
+      <c r="C102">
+        <v>0.07291619195187531</v>
+      </c>
+      <c r="D102">
+        <v>0.05956501440829402</v>
+      </c>
+      <c r="E102">
+        <v>6.194690265486726</v>
+      </c>
+      <c r="F102">
+        <v>36.36363636363637</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PALESTINE</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>237</v>
+      </c>
+      <c r="C103">
+        <v>0.07200473955247687</v>
+      </c>
+      <c r="D103">
+        <v>0.06375066406941739</v>
+      </c>
+      <c r="E103">
+        <v>19.09547738693467</v>
+      </c>
+      <c r="F103">
+        <v>2.155172413793104</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MOLDAVIE</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>232</v>
+      </c>
+      <c r="C104">
+        <v>0.07048565222014613</v>
+      </c>
+      <c r="D104">
+        <v>0.09530402305327045</v>
+      </c>
+      <c r="E104">
+        <v>-10.07751937984496</v>
+      </c>
+      <c r="F104">
+        <v>-43.13725490196079</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>COSTA RICA</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>222</v>
+      </c>
+      <c r="C105">
+        <v>0.06744747755548466</v>
+      </c>
+      <c r="D105">
+        <v>0.06986815203567462</v>
+      </c>
+      <c r="E105">
+        <v>1.36986301369863</v>
+      </c>
+      <c r="F105">
+        <v>29.06976744186047</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SOUDAN</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>219</v>
+      </c>
+      <c r="C106">
+        <v>0.06653602515608623</v>
+      </c>
+      <c r="D106">
+        <v>0.07630761305278749</v>
+      </c>
+      <c r="E106">
+        <v>-3.524229074889868</v>
+      </c>
+      <c r="F106">
+        <v>-22.06405693950178</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>BIELORUSSIE</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>219</v>
+      </c>
+      <c r="C107">
+        <v>0.06653602515608623</v>
+      </c>
+      <c r="D107">
+        <v>0.07019012508653026</v>
+      </c>
+      <c r="E107">
+        <v>0.4587155963302753</v>
+      </c>
+      <c r="F107">
+        <v>-20.93862815884476</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>KENYA</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>213</v>
+      </c>
+      <c r="C108">
+        <v>0.06471312035728934</v>
+      </c>
+      <c r="D108">
+        <v>0.05827712220487145</v>
+      </c>
+      <c r="E108">
+        <v>0.9478672985781991</v>
+      </c>
+      <c r="F108">
+        <v>18.33333333333333</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>CROATIE</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>205</v>
+      </c>
+      <c r="C109">
+        <v>0.06228258062556016</v>
+      </c>
+      <c r="D109">
+        <v>0.0660044754254069</v>
+      </c>
+      <c r="E109">
+        <v>3.535353535353535</v>
+      </c>
+      <c r="F109">
+        <v>3.535353535353535</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>IRAK</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>200</v>
+      </c>
+      <c r="C110">
+        <v>0.06076349329322943</v>
+      </c>
+      <c r="D110">
+        <v>0.07759550525621006</v>
+      </c>
+      <c r="E110">
+        <v>6.382978723404255</v>
+      </c>
+      <c r="F110">
+        <v>-31.27147766323024</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SRI LANKA</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>190</v>
+      </c>
+      <c r="C111">
+        <v>0.05772531862856796</v>
+      </c>
+      <c r="D111">
+        <v>0.06053093356086095</v>
+      </c>
+      <c r="E111">
+        <v>3.260869565217391</v>
+      </c>
+      <c r="F111">
+        <v>6.145251396648044</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>GUATEMALA</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>189</v>
+      </c>
+      <c r="C112">
+        <v>0.0574215011621018</v>
+      </c>
+      <c r="D112">
+        <v>0.05312555339118116</v>
+      </c>
+      <c r="E112">
+        <v>6.179775280898876</v>
+      </c>
+      <c r="F112">
+        <v>11.1764705882353</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>LETTONIE</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>178</v>
+      </c>
+      <c r="C113">
+        <v>0.05407950903097419</v>
+      </c>
+      <c r="D113">
+        <v>0.04475425406893443</v>
+      </c>
+      <c r="E113">
+        <v>31.85185185185185</v>
+      </c>
+      <c r="F113">
+        <v>32.83582089552239</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>JORDANIE</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>176</v>
+      </c>
+      <c r="C114">
+        <v>0.0534718740980419</v>
+      </c>
+      <c r="D114">
+        <v>0.05473541864545937</v>
+      </c>
+      <c r="E114">
+        <v>-2.762430939226519</v>
+      </c>
+      <c r="F114">
+        <v>17.33333333333334</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ISRAEL</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>171</v>
+      </c>
+      <c r="C115">
+        <v>0.05195278676571116</v>
+      </c>
+      <c r="D115">
+        <v>0.06053093356086095</v>
+      </c>
+      <c r="E115">
+        <v>-7.065217391304348</v>
+      </c>
+      <c r="F115">
+        <v>0.5882352941176471</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>HONDURAS</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>169</v>
+      </c>
+      <c r="C116">
+        <v>0.05134515183277887</v>
+      </c>
+      <c r="D116">
+        <v>0.05151568813690294</v>
+      </c>
+      <c r="E116">
+        <v>6.289308176100629</v>
+      </c>
+      <c r="F116">
+        <v>36.29032258064516</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>YEMEN</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>169</v>
+      </c>
+      <c r="C117">
+        <v>0.05134515183277887</v>
+      </c>
+      <c r="D117">
+        <v>0.06954617898481898</v>
+      </c>
+      <c r="E117">
+        <v>-9.62566844919786</v>
+      </c>
+      <c r="F117">
+        <v>-18.35748792270531</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MONACO</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>155</v>
+      </c>
+      <c r="C118">
+        <v>0.04709170730225281</v>
+      </c>
+      <c r="D118">
+        <v>0.0585990952557271</v>
+      </c>
+      <c r="E118">
+        <v>-17.5531914893617</v>
+      </c>
+      <c r="F118">
+        <v>-14.83516483516484</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MOZAMBIQUE</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>138</v>
+      </c>
+      <c r="C119">
+        <v>0.0419268103723283</v>
+      </c>
+      <c r="D119">
+        <v>0.0341291433906982</v>
+      </c>
+      <c r="E119">
+        <v>13.11475409836066</v>
+      </c>
+      <c r="F119">
+        <v>102.9411764705882</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>OUZBEKISTAN</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>137</v>
+      </c>
+      <c r="C120">
+        <v>0.04162299290586216</v>
+      </c>
+      <c r="D120">
+        <v>0.03895873915353285</v>
+      </c>
+      <c r="E120">
+        <v>2.238805970149254</v>
+      </c>
+      <c r="F120">
+        <v>3.787878787878788</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>CUBA</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>136</v>
+      </c>
+      <c r="C121">
+        <v>0.04131917543939601</v>
+      </c>
+      <c r="D121">
+        <v>0.04636411932321265</v>
+      </c>
+      <c r="E121">
+        <v>7.936507936507936</v>
+      </c>
+      <c r="F121">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ESTONIE</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>125</v>
+      </c>
+      <c r="C122">
+        <v>0.03797718330826839</v>
+      </c>
+      <c r="D122">
+        <v>0.02801165542444098</v>
+      </c>
+      <c r="E122">
+        <v>21.35922330097087</v>
+      </c>
+      <c r="F122">
+        <v>40.44943820224719</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MONGOLIE</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>116</v>
+      </c>
+      <c r="C123">
+        <v>0.03524282611007307</v>
+      </c>
+      <c r="D123">
+        <v>0.03123138593299741</v>
+      </c>
+      <c r="E123">
+        <v>2.654867256637168</v>
+      </c>
+      <c r="F123">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>REPUBLIQUE DOMINICAINE</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>115</v>
+      </c>
+      <c r="C124">
+        <v>0.03493900864360693</v>
+      </c>
+      <c r="D124">
+        <v>0.03928071220438849</v>
+      </c>
+      <c r="E124">
+        <v>-15.44117647058824</v>
+      </c>
+      <c r="F124">
+        <v>-28.125</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>URUGUAY</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>113</v>
+      </c>
+      <c r="C125">
+        <v>0.03433137371067463</v>
+      </c>
+      <c r="D125">
+        <v>0.03670492779754335</v>
+      </c>
+      <c r="E125">
+        <v>-12.4031007751938</v>
+      </c>
+      <c r="F125">
+        <v>17.70833333333334</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>COREE DU NORD</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>111</v>
+      </c>
+      <c r="C126">
+        <v>0.03372373877774233</v>
+      </c>
+      <c r="D126">
+        <v>0.03477308949240949</v>
+      </c>
+      <c r="E126">
+        <v>4.716981132075472</v>
+      </c>
+      <c r="F126">
+        <v>-31.90184049079755</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>LIBYE</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>106</v>
+      </c>
+      <c r="C127">
+        <v>0.0322046514454116</v>
+      </c>
+      <c r="D127">
+        <v>0.05505739169631502</v>
+      </c>
+      <c r="E127">
+        <v>-29.33333333333333</v>
+      </c>
+      <c r="F127">
+        <v>-61.02941176470588</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SLOVENIE</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>100</v>
+      </c>
+      <c r="C128">
+        <v>0.03038174664661471</v>
+      </c>
+      <c r="D128">
+        <v>0.03155335898385305</v>
+      </c>
+      <c r="E128">
+        <v>-7.407407407407407</v>
+      </c>
+      <c r="F128">
+        <v>-0.9900990099009901</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>KIRGHIZISTAN</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>99</v>
+      </c>
+      <c r="C129">
+        <v>0.03007792918014857</v>
+      </c>
+      <c r="D129">
+        <v>0.02768968237358533</v>
+      </c>
+      <c r="E129">
+        <v>8.791208791208792</v>
+      </c>
+      <c r="F129">
+        <v>23.75</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>KOWEIT</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>91</v>
+      </c>
+      <c r="C130">
+        <v>0.02764738944841939</v>
+      </c>
+      <c r="D130">
+        <v>0.03348519728898691</v>
+      </c>
+      <c r="E130">
+        <v>-10.7843137254902</v>
+      </c>
+      <c r="F130">
+        <v>-29.45736434108527</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>BOSNIE-HERZEGOVINE</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>87</v>
+      </c>
+      <c r="C131">
+        <v>0.0264321195825548</v>
+      </c>
+      <c r="D131">
+        <v>0.02511389796674018</v>
+      </c>
+      <c r="E131">
+        <v>-17.14285714285714</v>
+      </c>
+      <c r="F131">
+        <v>-33.07692307692307</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MACEDOINE</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>84</v>
+      </c>
+      <c r="C132">
+        <v>0.02552066718315636</v>
+      </c>
+      <c r="D132">
+        <v>0.03445111644155384</v>
+      </c>
+      <c r="E132">
+        <v>-6.666666666666667</v>
+      </c>
+      <c r="F132">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>NICARAGUA</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>75</v>
+      </c>
+      <c r="C133">
+        <v>0.02278630998496103</v>
+      </c>
+      <c r="D133">
+        <v>0.0267237632210184</v>
+      </c>
+      <c r="E133">
+        <v>1.351351351351351</v>
+      </c>
+      <c r="F133">
+        <v>8.695652173913043</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>BIRMANIE</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>75</v>
+      </c>
+      <c r="C134">
+        <v>0.02278630998496103</v>
+      </c>
+      <c r="D134">
+        <v>0.02253811355989504</v>
+      </c>
+      <c r="E134">
+        <v>11.94029850746269</v>
+      </c>
+      <c r="F134">
+        <v>97.36842105263158</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>PANAMA</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>71</v>
+      </c>
+      <c r="C135">
+        <v>0.02157104011909645</v>
+      </c>
+      <c r="D135">
+        <v>0.02060627525476117</v>
+      </c>
+      <c r="E135">
+        <v>-4.054054054054054</v>
+      </c>
+      <c r="F135">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>OUGANDA</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>69</v>
+      </c>
+      <c r="C136">
+        <v>0.02096340518616415</v>
+      </c>
+      <c r="D136">
+        <v>0.01835246389877167</v>
+      </c>
+      <c r="E136">
+        <v>-12.65822784810127</v>
+      </c>
+      <c r="F136">
+        <v>-28.8659793814433</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>OMAN</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>68</v>
+      </c>
+      <c r="C137">
+        <v>0.02065958771969801</v>
+      </c>
+      <c r="D137">
+        <v>0.02382600576331761</v>
+      </c>
+      <c r="E137">
+        <v>-5.555555555555555</v>
+      </c>
+      <c r="F137">
+        <v>-10.52631578947368</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>PARAGUAY</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>68</v>
+      </c>
+      <c r="C138">
+        <v>0.02065958771969801</v>
+      </c>
+      <c r="D138">
+        <v>0.02318205966160632</v>
+      </c>
+      <c r="E138">
+        <v>-2.857142857142857</v>
+      </c>
+      <c r="F138">
+        <v>-18.07228915662651</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>LAOS</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>62</v>
+      </c>
+      <c r="C139">
+        <v>0.01883668292090112</v>
+      </c>
+      <c r="D139">
+        <v>0.02157219440732811</v>
+      </c>
+      <c r="E139">
+        <v>-15.06849315068493</v>
+      </c>
+      <c r="F139">
+        <v>-21.51898734177215</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>NOUVELLE ZELANDE</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>61</v>
+      </c>
+      <c r="C140">
+        <v>0.01853286545443497</v>
+      </c>
+      <c r="D140">
+        <v>0.01545470644107088</v>
+      </c>
+      <c r="E140">
+        <v>-16.43835616438356</v>
+      </c>
+      <c r="F140">
+        <v>-31.46067415730337</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ZIMBABWE</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>59</v>
+      </c>
+      <c r="C141">
+        <v>0.01792523052150268</v>
+      </c>
+      <c r="D141">
+        <v>0.02157219440732811</v>
+      </c>
+      <c r="E141">
+        <v>-14.49275362318841</v>
+      </c>
+      <c r="F141">
+        <v>9.25925925925926</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>KOSOVO</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>58</v>
+      </c>
+      <c r="C142">
+        <v>0.01762141305503653</v>
+      </c>
+      <c r="D142">
+        <v>0.02189416745818375</v>
+      </c>
+      <c r="E142">
+        <v>-13.43283582089552</v>
+      </c>
+      <c r="F142">
+        <v>-47.74774774774775</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>GUINEE EQUATORIALE</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>50</v>
+      </c>
+      <c r="C143">
+        <v>0.01519087332330736</v>
+      </c>
+      <c r="D143">
+        <v>0.01803049084791603</v>
+      </c>
+      <c r="E143">
+        <v>2.040816326530612</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>BAHREIN</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>49</v>
+      </c>
+      <c r="C144">
+        <v>0.01488705585684121</v>
+      </c>
+      <c r="D144">
+        <v>0.02157219440732811</v>
+      </c>
+      <c r="E144">
+        <v>13.95348837209302</v>
+      </c>
+      <c r="F144">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CAP-VERT</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>43</v>
+      </c>
+      <c r="C145">
+        <v>0.01306415105804433</v>
+      </c>
+      <c r="D145">
+        <v>0.01352286813593702</v>
+      </c>
+      <c r="E145">
+        <v>-8.51063829787234</v>
+      </c>
+      <c r="F145">
+        <v>-21.81818181818182</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>JAMAIQUE</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>42</v>
+      </c>
+      <c r="C146">
+        <v>0.01276033359157818</v>
+      </c>
+      <c r="D146">
+        <v>0.01448878728850395</v>
+      </c>
+      <c r="E146">
+        <v>44.82758620689656</v>
+      </c>
+      <c r="F146">
+        <v>-6.666666666666667</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>TANZANIE</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>40</v>
+      </c>
+      <c r="C147">
+        <v>0.01215269865864588</v>
+      </c>
+      <c r="D147">
+        <v>0.01867443694962731</v>
+      </c>
+      <c r="E147">
+        <v>-31.03448275862069</v>
+      </c>
+      <c r="F147">
+        <v>-14.8936170212766</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>DOMINIQUE</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>38</v>
+      </c>
+      <c r="C148">
+        <v>0.01154506372571359</v>
+      </c>
+      <c r="D148">
+        <v>0.01384484118679266</v>
+      </c>
+      <c r="E148">
+        <v>-17.39130434782609</v>
+      </c>
+      <c r="F148">
+        <v>-13.63636363636363</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>MONTENEGRO</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>38</v>
+      </c>
+      <c r="C149">
+        <v>0.01154506372571359</v>
+      </c>
+      <c r="D149">
+        <v>0.01416681423764831</v>
+      </c>
+      <c r="E149">
+        <v>-7.317073170731707</v>
+      </c>
+      <c r="F149">
+        <v>-11.62790697674419</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>MALTE</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>36</v>
+      </c>
+      <c r="C150">
+        <v>0.0109374287927813</v>
+      </c>
+      <c r="D150">
+        <v>0.01255694898337009</v>
+      </c>
+      <c r="E150">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="F150">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>GUINEE-BISSAO</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>34</v>
+      </c>
+      <c r="C151">
+        <v>0.010329793859849</v>
+      </c>
+      <c r="D151">
+        <v>0.009337218474813657</v>
+      </c>
+      <c r="E151">
+        <v>9.67741935483871</v>
+      </c>
+      <c r="F151">
+        <v>3.03030303030303</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ISLANDE</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>32</v>
+      </c>
+      <c r="C152">
+        <v>0.009722158926916708</v>
+      </c>
+      <c r="D152">
+        <v>0.01094708372909188</v>
+      </c>
+      <c r="E152">
+        <v>3.225806451612903</v>
+      </c>
+      <c r="F152">
+        <v>-11.11111111111111</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ILES MARSHALL</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>30</v>
+      </c>
+      <c r="C153">
+        <v>0.009114523993984413</v>
+      </c>
+      <c r="D153">
+        <v>0.008693272373102372</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+      <c r="F153">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>SOMALIE</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>30</v>
+      </c>
+      <c r="C154">
+        <v>0.009114523993984413</v>
+      </c>
+      <c r="D154">
+        <v>0.009659191525669301</v>
+      </c>
+      <c r="E154">
+        <v>-14.28571428571428</v>
+      </c>
+      <c r="F154">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TADJIKISTAN</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>28</v>
+      </c>
+      <c r="C155">
+        <v>0.00850688906105212</v>
+      </c>
+      <c r="D155">
+        <v>0.007083407118824154</v>
+      </c>
+      <c r="E155">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="F155">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>GAMBIE</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>26</v>
+      </c>
+      <c r="C156">
+        <v>0.007899254128119825</v>
+      </c>
+      <c r="D156">
+        <v>0.003863676610267721</v>
+      </c>
+      <c r="E156">
+        <v>23.80952380952381</v>
+      </c>
+      <c r="F156">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SAINTE-LUCIE</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>25</v>
+      </c>
+      <c r="C157">
+        <v>0.007595436661653679</v>
+      </c>
+      <c r="D157">
+        <v>0.01255694898337009</v>
+      </c>
+      <c r="E157">
+        <v>-30.55555555555556</v>
+      </c>
+      <c r="F157">
+        <v>-32.43243243243244</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>TRINITE-ET-TOBAGO</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>24</v>
+      </c>
+      <c r="C158">
+        <v>0.007291619195187531</v>
+      </c>
+      <c r="D158">
+        <v>0.01062511067823623</v>
+      </c>
+      <c r="E158">
+        <v>-25</v>
+      </c>
+      <c r="F158">
+        <v>-22.58064516129032</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>SIERRA LEONE</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>24</v>
+      </c>
+      <c r="C159">
+        <v>0.007291619195187531</v>
+      </c>
+      <c r="D159">
+        <v>0.003863676610267721</v>
+      </c>
+      <c r="E159">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="F159">
+        <v>71.42857142857143</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>GRENADE</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>22</v>
+      </c>
+      <c r="C160">
+        <v>0.006683984262255237</v>
+      </c>
+      <c r="D160">
+        <v>0.004507622711979007</v>
+      </c>
+      <c r="E160">
+        <v>37.5</v>
+      </c>
+      <c r="F160">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ZAMBIE</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>21</v>
+      </c>
+      <c r="C161">
+        <v>0.00638016679578909</v>
+      </c>
+      <c r="D161">
+        <v>0.007083407118824154</v>
+      </c>
+      <c r="E161">
+        <v>5</v>
+      </c>
+      <c r="F161">
+        <v>-19.23076923076923</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>TURKMENISTAN</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>19</v>
+      </c>
+      <c r="C162">
+        <v>0.005772531862856796</v>
+      </c>
+      <c r="D162">
+        <v>0.006761434067968511</v>
+      </c>
+      <c r="E162">
+        <v>-9.523809523809524</v>
+      </c>
+      <c r="F162">
+        <v>-34.48275862068966</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>MALAWI</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>18</v>
+      </c>
+      <c r="C163">
+        <v>0.005468714396390648</v>
+      </c>
+      <c r="D163">
+        <v>0.005473541864545938</v>
+      </c>
+      <c r="E163">
+        <v>12.5</v>
+      </c>
+      <c r="F163">
+        <v>157.1428571428571</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>BAHAMAS</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>14</v>
+      </c>
+      <c r="C164">
+        <v>0.00425344453052606</v>
+      </c>
+      <c r="D164">
+        <v>0.003541703559412077</v>
+      </c>
+      <c r="E164">
+        <v>40</v>
+      </c>
+      <c r="F164">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>MALDIVES</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>14</v>
+      </c>
+      <c r="C165">
+        <v>0.00425344453052606</v>
+      </c>
+      <c r="D165">
+        <v>0.003541703559412077</v>
+      </c>
+      <c r="E165">
+        <v>55.55555555555556</v>
+      </c>
+      <c r="F165">
+        <v>-6.666666666666667</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>SAINT-CHRISTOPHE-ET-NIEVES</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>13</v>
+      </c>
+      <c r="C166">
+        <v>0.003949627064059913</v>
+      </c>
+      <c r="D166">
+        <v>0.0006439461017112867</v>
+      </c>
+      <c r="E166">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="F166">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>LIBERIA</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>12</v>
+      </c>
+      <c r="C167">
+        <v>0.003645809597593766</v>
+      </c>
+      <c r="D167">
+        <v>0.002253811355989504</v>
+      </c>
+      <c r="E167">
+        <v>20</v>
+      </c>
+      <c r="F167">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ERYTHREE</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>11</v>
+      </c>
+      <c r="C168">
+        <v>0.003341992131127619</v>
+      </c>
+      <c r="D168">
+        <v>0.005151568813690294</v>
+      </c>
+      <c r="E168">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="F168">
+        <v>-21.42857142857143</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>NAMIBIE</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>11</v>
+      </c>
+      <c r="C169">
+        <v>0.003341992131127619</v>
+      </c>
+      <c r="D169">
+        <v>0.002575784406845147</v>
+      </c>
+      <c r="E169">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="F169">
+        <v>57.14285714285714</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>SAO TOME-ET-PRINCIPE</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>10</v>
+      </c>
+      <c r="C170">
+        <v>0.003038174664661471</v>
+      </c>
+      <c r="D170">
+        <v>0.004507622711979007</v>
+      </c>
+      <c r="E170">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="F170">
+        <v>66.66666666666666</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ANTIGUA-ET-BARBUDA</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>10</v>
+      </c>
+      <c r="C171">
+        <v>0.003038174664661471</v>
+      </c>
+      <c r="D171">
+        <v>0.00289775745770079</v>
+      </c>
+      <c r="E171">
+        <v>-9.090909090909092</v>
+      </c>
+      <c r="F171">
+        <v>-9.090909090909092</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>GUYANA</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>9</v>
+      </c>
+      <c r="C172">
+        <v>0.002734357198195324</v>
+      </c>
+      <c r="D172">
+        <v>0.002253811355989504</v>
+      </c>
+      <c r="E172">
+        <v>-18.18181818181818</v>
+      </c>
+      <c r="F172">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>BOTSWANA</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>9</v>
+      </c>
+      <c r="C173">
+        <v>0.002734357198195324</v>
+      </c>
+      <c r="D173">
+        <v>0.00482959576283465</v>
+      </c>
+      <c r="E173">
+        <v>-25</v>
+      </c>
+      <c r="F173">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>SEYCHELLES</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>9</v>
+      </c>
+      <c r="C174">
+        <v>0.002734357198195324</v>
+      </c>
+      <c r="D174">
+        <v>0.005473541864545938</v>
+      </c>
+      <c r="E174">
+        <v>-30.76923076923077</v>
+      </c>
+      <c r="F174">
+        <v>-52.63157894736842</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>LESOTHO</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>8</v>
+      </c>
+      <c r="C175">
+        <v>0.002430539731729177</v>
+      </c>
+      <c r="D175">
+        <v>0.004185649661123364</v>
+      </c>
+      <c r="E175">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="F175">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>BRUNEI</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>8</v>
+      </c>
+      <c r="C176">
+        <v>0.002430539731729177</v>
+      </c>
+      <c r="D176">
+        <v>0.002575784406845147</v>
+      </c>
+      <c r="E176">
+        <v>-27.27272727272727</v>
+      </c>
+      <c r="F176">
+        <v>-33.33333333333333</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>VANUATU</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>7</v>
+      </c>
+      <c r="C177">
+        <v>0.00212672226526303</v>
+      </c>
+      <c r="D177">
+        <v>0.002575784406845147</v>
+      </c>
+      <c r="E177">
+        <v>-22.22222222222222</v>
+      </c>
+      <c r="F177">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>SURINAME</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>6</v>
+      </c>
+      <c r="C178">
+        <v>0.001822904798796883</v>
+      </c>
+      <c r="D178">
+        <v>0.0006439461017112867</v>
+      </c>
+      <c r="E178">
+        <v>20</v>
+      </c>
+      <c r="F178">
+        <v>-57.14285714285714</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>SAINT-MARIN</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>5</v>
+      </c>
+      <c r="C179">
+        <v>0.001519087332330736</v>
+      </c>
+      <c r="D179">
+        <v>0.001609865254278217</v>
+      </c>
+      <c r="E179">
+        <v>-28.57142857142857</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>FIDJI</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>5</v>
+      </c>
+      <c r="C180">
+        <v>0.001519087332330736</v>
+      </c>
+      <c r="D180">
+        <v>0.00193183830513386</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
+      <c r="F180">
+        <v>-16.66666666666666</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>BHOUTAN</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>5</v>
+      </c>
+      <c r="C181">
+        <v>0.001519087332330736</v>
+      </c>
+      <c r="D181">
+        <v>0.0006439461017112867</v>
+      </c>
+      <c r="E181">
+        <v>150</v>
+      </c>
+      <c r="F181">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>SWAZILAND</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>2</v>
+      </c>
+      <c r="C182">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D182">
+        <v>0.0006439461017112867</v>
+      </c>
+      <c r="E182">
+        <v>-60</v>
+      </c>
+      <c r="F182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>TIMOR ORIENTAL</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>2</v>
+      </c>
+      <c r="C183">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D183">
+        <v>0.0006439461017112867</v>
+      </c>
+      <c r="E183">
+        <v>0</v>
+      </c>
+      <c r="F183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>LIECHTENSTEIN</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>2</v>
+      </c>
+      <c r="C184">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D184">
+        <v>0.0006439461017112867</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>BELIZE</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>2</v>
+      </c>
+      <c r="C185">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D185">
+        <v>0.0006439461017112867</v>
+      </c>
+      <c r="E185">
+        <v>0</v>
+      </c>
+      <c r="F185">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>SAINT-VINCENT-ET-LES-GRENADINES</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>2</v>
+      </c>
+      <c r="C186">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D186">
+        <v>0.0006439461017112867</v>
+      </c>
+      <c r="E186">
+        <v>-60</v>
+      </c>
+      <c r="F186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>KIRIBATI</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>2</v>
+      </c>
+      <c r="C187">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>TONGA</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>2</v>
+      </c>
+      <c r="C188">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D188">
+        <v>0.0006439461017112867</v>
+      </c>
+      <c r="E188">
+        <v>0</v>
+      </c>
+      <c r="F188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>TUVALU</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>2</v>
+      </c>
+      <c r="C189">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="E189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ACORES</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>2</v>
+      </c>
+      <c r="C190">
+        <v>0.0006076349329322943</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BARBADE</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>2</v>
+      </c>
+      <c r="C191">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D191">
+        <v>0.0006439461017112867</v>
+      </c>
+      <c r="E191">
+        <v>0</v>
+      </c>
+      <c r="F191">
+        <v>-71.42857142857143</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>MACAO</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>2</v>
+      </c>
+      <c r="C192">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="E192">
+        <v>0</v>
+      </c>
+      <c r="F192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>SANS NATIONALITE</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>2</v>
+      </c>
+      <c r="C193">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D193">
+        <v>0.002253811355989504</v>
+      </c>
+      <c r="E193">
+        <v>-66.66666666666666</v>
+      </c>
+      <c r="F193">
+        <v>-81.81818181818183</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>REP. DES ILES PALAOS</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>2</v>
+      </c>
+      <c r="C194">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D194">
+        <v>0.0006439461017112867</v>
+      </c>
+      <c r="E194">
+        <v>0</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>VATICAN</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>2</v>
+      </c>
+      <c r="C195">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D195">
+        <v>0.001609865254278217</v>
+      </c>
+      <c r="E195">
+        <v>-83.33333333333334</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>PAPOUASIE-NOUVELLE-GUINEE</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>2</v>
+      </c>
+      <c r="C196">
+        <v>0.0006076349329322943</v>
+      </c>
+      <c r="D196">
+        <v>0.0006439461017112867</v>
+      </c>
+      <c r="E196">
+        <v>0</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>MICRONESIE</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="F197">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SAMOA OCCIDENTALES</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="F198">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ILES SALOMON</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>0.0006439461017112867</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>NAURU</t>
+        </is>
+      </c>
+      <c r="D200">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -598,7 +4866,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -609,12 +4877,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>effectif</t>
+          <t>part</t>
         </is>
       </c>
     </row>
@@ -624,133 +4887,88 @@
           <t>MAROC</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Université</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>18488</v>
+      <c r="B2">
+        <v>0.1083656139391454</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MAROC</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>École de commerce</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>6899</v>
+          <t>ALGERIE</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.08408148384450623</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MAROC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>École d'ingénieurs (hors université)</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>4215</v>
+          <t>CHINE</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.07052514849078674</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MAROC</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Commerce + Ingénieurs</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>11114</v>
+          <t>SENEGAL</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.04896929924501359</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHINE</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Université</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>11161</v>
+          <t>ITALIE</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.04070242598246973</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHINE</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>École de commerce</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>7305</v>
+          <t>TUNISIE</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.03946285071928785</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHINE</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>École d'ingénieurs (hors université)</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>1156</v>
+          <t>CAMEROUN</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.03086177824363123</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHINE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Commerce + Ingénieurs</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>8461</v>
+          <t>COTE D'IVOIRE</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.03068860228774552</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INDE</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Université</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>1590</v>
+          <t>LIBAN</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.02875328502635616</v>
       </c>
     </row>
     <row r="11">
@@ -759,463 +4977,8 @@
           <t>INDE</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>École de commerce</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>5331</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>INDE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>École d'ingénieurs (hors université)</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>INDE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Commerce + Ingénieurs</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>5518</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CAMEROUN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Université</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>3840</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CAMEROUN</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>École de commerce</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>2835</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CAMEROUN</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>École d'ingénieurs (hors université)</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CAMEROUN</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Commerce + Ingénieurs</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>4618</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ITALIE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Université</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>7806</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ITALIE</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>École de commerce</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>3220</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ITALIE</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>École d'ingénieurs (hors université)</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ITALIE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Commerce + Ingénieurs</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>3490</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>COTE D'IVOIRE</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Université</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>5572</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>COTE D'IVOIRE</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>École de commerce</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>2453</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>COTE D'IVOIRE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>École d'ingénieurs (hors université)</t>
-        </is>
-      </c>
-      <c r="C24">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>COTE D'IVOIRE</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Commerce + Ingénieurs</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>3011</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TUNISIE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Université</t>
-        </is>
-      </c>
-      <c r="C26">
-        <v>8091</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TUNISIE</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>École de commerce</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TUNISIE</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>École d'ingénieurs (hors université)</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TUNISIE</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Commerce + Ingénieurs</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>2613</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>SENEGAL</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Université</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>11748</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>SENEGAL</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>École de commerce</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>SENEGAL</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>École d'ingénieurs (hors université)</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>SENEGAL</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Commerce + Ingénieurs</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>2135</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LIBAN</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Université</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>6250</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LIBAN</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>École de commerce</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>LIBAN</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>École d'ingénieurs (hors université)</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>LIBAN</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Commerce + Ingénieurs</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>1799</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ALGERIE</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Université</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>23766</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ALGERIE</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>École de commerce</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>1416</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ALGERIE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>École d'ingénieurs (hors université)</t>
-        </is>
-      </c>
-      <c r="C40">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ALGERIE</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Commerce + Ingénieurs</t>
-        </is>
-      </c>
-      <c r="C41">
-        <v>1786</v>
+      <c r="B11">
+        <v>0.02551459083382704</v>
       </c>
     </row>
   </sheetData>
@@ -1241,6 +5004,633 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>effectif</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MAROC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Université</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>18488</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MAROC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>École de commerce</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>6899</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MAROC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>École d'ingénieurs (hors université)</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>4215</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MAROC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Commerce + Ingénieurs</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>11114</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CHINE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Université</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>11161</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CHINE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>École de commerce</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>7305</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CHINE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>École d'ingénieurs (hors université)</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CHINE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Commerce + Ingénieurs</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>8461</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>INDE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Université</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>INDE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>École de commerce</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>5331</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>INDE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>École d'ingénieurs (hors université)</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>INDE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Commerce + Ingénieurs</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>5518</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CAMEROUN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Université</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CAMEROUN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>École de commerce</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CAMEROUN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>École d'ingénieurs (hors université)</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CAMEROUN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Commerce + Ingénieurs</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>4618</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ITALIE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Université</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>7806</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ITALIE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>École de commerce</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ITALIE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>École d'ingénieurs (hors université)</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ITALIE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Commerce + Ingénieurs</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>COTE D'IVOIRE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Université</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>5572</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>COTE D'IVOIRE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>École de commerce</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>COTE D'IVOIRE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>École d'ingénieurs (hors université)</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>COTE D'IVOIRE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Commerce + Ingénieurs</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TUNISIE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Université</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>8091</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TUNISIE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>École de commerce</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TUNISIE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>École d'ingénieurs (hors université)</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TUNISIE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Commerce + Ingénieurs</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SENEGAL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Université</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>11748</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SENEGAL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>École de commerce</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SENEGAL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>École d'ingénieurs (hors université)</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SENEGAL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Commerce + Ingénieurs</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LIBAN</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Université</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>6250</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LIBAN</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>École de commerce</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LIBAN</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>École d'ingénieurs (hors université)</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LIBAN</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Commerce + Ingénieurs</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ALGERIE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Université</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>23766</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ALGERIE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>École de commerce</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ALGERIE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>École d'ingénieurs (hors université)</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ALGERIE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Commerce + Ingénieurs</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>1786</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nationalite</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>part</t>
         </is>
       </c>
